--- a/project-tron-version-2/nexus-combined-project-tron-version-2-weeks-14-26-38-50-seed1-10reps.xlsx
+++ b/project-tron-version-2/nexus-combined-project-tron-version-2-weeks-14-26-38-50-seed1-10reps.xlsx
@@ -36842,7 +36842,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:21 UTC</t>
+          <t>2026-10-28 11:45 UTC</t>
         </is>
       </c>
     </row>
